--- a/artfynd/A 2324-2025 artfynd.xlsx
+++ b/artfynd/A 2324-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122217512</v>
+        <v>122217547</v>
       </c>
       <c r="B2" t="n">
-        <v>57744</v>
+        <v>97132</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>221946</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582451</v>
+        <v>582438</v>
       </c>
       <c r="R2" t="n">
-        <v>6385098</v>
+        <v>6385112</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122217547</v>
+        <v>122217512</v>
       </c>
       <c r="B3" t="n">
-        <v>97132</v>
+        <v>57744</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582438</v>
+        <v>582451</v>
       </c>
       <c r="R3" t="n">
-        <v>6385112</v>
+        <v>6385098</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 2324-2025 artfynd.xlsx
+++ b/artfynd/A 2324-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122217547</v>
+        <v>122217512</v>
       </c>
       <c r="B2" t="n">
-        <v>97132</v>
+        <v>57744</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582438</v>
+        <v>582451</v>
       </c>
       <c r="R2" t="n">
-        <v>6385112</v>
+        <v>6385098</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122217512</v>
+        <v>122217547</v>
       </c>
       <c r="B3" t="n">
-        <v>57744</v>
+        <v>97142</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>221946</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582451</v>
+        <v>582438</v>
       </c>
       <c r="R3" t="n">
-        <v>6385098</v>
+        <v>6385112</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 2324-2025 artfynd.xlsx
+++ b/artfynd/A 2324-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122217512</v>
+        <v>122217547</v>
       </c>
       <c r="B2" t="n">
-        <v>57744</v>
+        <v>97154</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>221946</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582451</v>
+        <v>582438</v>
       </c>
       <c r="R2" t="n">
-        <v>6385098</v>
+        <v>6385112</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122217547</v>
+        <v>122217512</v>
       </c>
       <c r="B3" t="n">
-        <v>97142</v>
+        <v>57749</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582438</v>
+        <v>582451</v>
       </c>
       <c r="R3" t="n">
-        <v>6385112</v>
+        <v>6385098</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 2324-2025 artfynd.xlsx
+++ b/artfynd/A 2324-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122217547</v>
+        <v>122217512</v>
       </c>
       <c r="B2" t="n">
-        <v>97154</v>
+        <v>57749</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582438</v>
+        <v>582451</v>
       </c>
       <c r="R2" t="n">
-        <v>6385112</v>
+        <v>6385098</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122217512</v>
+        <v>122217547</v>
       </c>
       <c r="B3" t="n">
-        <v>57749</v>
+        <v>97159</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>221946</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582451</v>
+        <v>582438</v>
       </c>
       <c r="R3" t="n">
-        <v>6385098</v>
+        <v>6385112</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 2324-2025 artfynd.xlsx
+++ b/artfynd/A 2324-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122217512</v>
+        <v>122217547</v>
       </c>
       <c r="B2" t="n">
-        <v>57749</v>
+        <v>97168</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
+        <v>221946</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582451</v>
+        <v>582438</v>
       </c>
       <c r="R2" t="n">
-        <v>6385098</v>
+        <v>6385112</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122217547</v>
+        <v>122217512</v>
       </c>
       <c r="B3" t="n">
-        <v>97159</v>
+        <v>57749</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +798,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Mattlummer</t>
-        </is>
+        <v>103015</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582438</v>
+        <v>582451</v>
       </c>
       <c r="R3" t="n">
-        <v>6385112</v>
+        <v>6385098</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 2324-2025 artfynd.xlsx
+++ b/artfynd/A 2324-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122217547</v>
+        <v>122217512</v>
       </c>
       <c r="B2" t="n">
-        <v>97168</v>
+        <v>57753</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>103015</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582438</v>
+        <v>582451</v>
       </c>
       <c r="R2" t="n">
-        <v>6385112</v>
+        <v>6385098</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122217512</v>
+        <v>122217547</v>
       </c>
       <c r="B3" t="n">
-        <v>57749</v>
+        <v>97181</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,16 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>221946</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582451</v>
+        <v>582438</v>
       </c>
       <c r="R3" t="n">
-        <v>6385098</v>
+        <v>6385112</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 2324-2025 artfynd.xlsx
+++ b/artfynd/A 2324-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>122217547</v>
       </c>
       <c r="B3" t="n">
-        <v>97181</v>
+        <v>97194</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 2324-2025 artfynd.xlsx
+++ b/artfynd/A 2324-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122217512</v>
+        <v>122217547</v>
       </c>
       <c r="B2" t="n">
-        <v>57753</v>
+        <v>97194</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>221946</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582451</v>
+        <v>582438</v>
       </c>
       <c r="R2" t="n">
-        <v>6385098</v>
+        <v>6385112</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122217547</v>
+        <v>122217512</v>
       </c>
       <c r="B3" t="n">
-        <v>97194</v>
+        <v>57753</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582438</v>
+        <v>582451</v>
       </c>
       <c r="R3" t="n">
-        <v>6385112</v>
+        <v>6385098</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 2324-2025 artfynd.xlsx
+++ b/artfynd/A 2324-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122217547</v>
+        <v>122217512</v>
       </c>
       <c r="B2" t="n">
-        <v>97194</v>
+        <v>57753</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582438</v>
+        <v>582451</v>
       </c>
       <c r="R2" t="n">
-        <v>6385112</v>
+        <v>6385098</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122217512</v>
+        <v>122217547</v>
       </c>
       <c r="B3" t="n">
-        <v>57753</v>
+        <v>97197</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>221946</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582451</v>
+        <v>582438</v>
       </c>
       <c r="R3" t="n">
-        <v>6385098</v>
+        <v>6385112</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
